--- a/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,26</t>
+          <t>13,9; 24,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 20,64</t>
+          <t>13,59; 21,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,7; 21,26</t>
+          <t>14,73; 21,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 17,64</t>
+          <t>9,94; 17,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,34</t>
+          <t>12,79; 18,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 16,85</t>
+          <t>12,16; 16,99</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,16; 35,54</t>
+          <t>25,12; 35,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,64; 34,98</t>
+          <t>26,69; 35,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,26; 33,77</t>
+          <t>27,34; 33,74</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,59; 37,32</t>
+          <t>24,93; 38,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,56; 59,52</t>
+          <t>24,67; 61,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,21; 52,65</t>
+          <t>27,09; 52,92</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,54; 34,96</t>
+          <t>22,22; 34,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 20,75</t>
+          <t>8,79; 20,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 24,66</t>
+          <t>14,45; 25,06</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,71; 38,25</t>
+          <t>27,84; 38,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,61; 32,28</t>
+          <t>23,1; 31,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,02; 33,9</t>
+          <t>26,92; 34,12</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,35; 39,5</t>
+          <t>29,99; 39,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,57; 39,3</t>
+          <t>14,05; 39,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 37,46</t>
+          <t>19,94; 37,55</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,43; 86,91</t>
+          <t>28,59; 86,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,08; 90,14</t>
+          <t>86,06; 90,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,35; 87,59</t>
+          <t>45,09; 87,66</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,03; 39,9</t>
+          <t>28,49; 40,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,37; 41,33</t>
+          <t>30,99; 41,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,85</t>
+          <t>32,72; 40,09</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43346; 75560</t>
+          <t>43291; 75244</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38957; 59790</t>
+          <t>39360; 61223</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88364; 127809</t>
+          <t>88539; 128767</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50380; 91424</t>
+          <t>51521; 91607</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66546; 94442</t>
+          <t>65844; 93722</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123496; 174167</t>
+          <t>125635; 175546</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79526; 112331</t>
+          <t>79381; 111623</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93020; 122137</t>
+          <t>93171; 122653</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181320; 224658</t>
+          <t>181874; 224447</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76851; 116634</t>
+          <t>77922; 119164</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116834; 283169</t>
+          <t>117378; 294660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>214460; 414992</t>
+          <t>213569; 417160</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40290; 62483</t>
+          <t>39715; 62212</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22090; 53692</t>
+          <t>22747; 53584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62016; 107908</t>
+          <t>63241; 109650</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74712; 103137</t>
+          <t>75068; 103423</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60687; 82987</t>
+          <t>59385; 81794</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>142311; 178555</t>
+          <t>141776; 179698</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>189495; 246606</t>
+          <t>187223; 243517</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>132202; 333771</t>
+          <t>119350; 333159</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266772; 551983</t>
+          <t>293813; 553292</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>264061; 807180</t>
+          <t>265495; 807258</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>617788; 646959</t>
+          <t>617646; 645979</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>763212; 1442114</t>
+          <t>742432; 1443239</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>969935; 1380426</t>
+          <t>985624; 1385169</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1127339; 1534209</t>
+          <t>1150352; 1537056</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2314614; 2858358</t>
+          <t>2346364; 2875222</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 24,16</t>
+          <t>17,27; 27,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 21,14</t>
+          <t>17,84; 26,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,73; 21,42</t>
+          <t>18,81; 24,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 17,67</t>
+          <t>9,9; 17,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 18,2</t>
+          <t>13,1; 18,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,16; 16,99</t>
+          <t>12,36; 16,83</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,12; 35,32</t>
+          <t>26,21; 36,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,69; 35,13</t>
+          <t>27,59; 36,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,34; 33,74</t>
+          <t>28,46; 34,94</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,93; 38,13</t>
+          <t>24,16; 35,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,67; 61,94</t>
+          <t>25,22; 34,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,09; 52,92</t>
+          <t>26,31; 33,17</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,22; 34,81</t>
+          <t>24,78; 36,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,79; 20,71</t>
+          <t>17,15; 25,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,45; 25,06</t>
+          <t>21,68; 28,81</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,84; 38,36</t>
+          <t>29,26; 39,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,1; 31,82</t>
+          <t>23,99; 33,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,92; 34,12</t>
+          <t>28,14; 34,98</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,99; 39,01</t>
+          <t>30,55; 38,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,05; 39,23</t>
+          <t>35,37; 42,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,94; 37,55</t>
+          <t>34,37; 39,54</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,59; 86,92</t>
+          <t>83,48; 88,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,06; 90,0</t>
+          <t>85,38; 89,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,09; 87,66</t>
+          <t>85,06; 88,59</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,49; 40,04</t>
+          <t>38,93; 42,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,4</t>
+          <t>39,78; 42,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,72; 40,09</t>
+          <t>39,82; 42,08</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57789</t>
+          <t>69560</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106447</t>
+          <t>138114</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43291; 75244</t>
+          <t>55064; 86187</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39360; 61223</t>
+          <t>56371; 82689</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88539; 128767</t>
+          <t>119439; 158230</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68379</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80123</t>
+          <t>85182</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148502</t>
+          <t>155925</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51521; 91607</t>
+          <t>52524; 92173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65844; 93722</t>
+          <t>71617; 100091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125635; 175546</t>
+          <t>133107; 181281</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94849</t>
+          <t>98152</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>107374</t>
+          <t>113300</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202222</t>
+          <t>211452</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79381; 111623</t>
+          <t>82834; 113975</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93171; 122653</t>
+          <t>98308; 128761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181874; 224447</t>
+          <t>191359; 234907</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>97773</t>
+          <t>110122</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>176419</t>
+          <t>124189</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274192</t>
+          <t>234312</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77922; 119164</t>
+          <t>90136; 132695</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117378; 294660</t>
+          <t>106399; 144217</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>213569; 417160</t>
+          <t>209167; 263747</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>61697</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>47214</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90414</t>
+          <t>108910</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39715; 62212</t>
+          <t>50972; 75465</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22747; 53584</t>
+          <t>39269; 57795</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63241; 109650</t>
+          <t>94220; 125224</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>88970</t>
+          <t>92974</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>70874</t>
+          <t>75454</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159844</t>
+          <t>168429</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>75068; 103423</t>
+          <t>79213; 107302</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>59385; 81794</t>
+          <t>63271; 87924</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141776; 179698</t>
+          <t>150421; 186927</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>216977</t>
+          <t>249165</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>246792</t>
+          <t>298179</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>463770</t>
+          <t>547344</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>187223; 243517</t>
+          <t>219862; 277814</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>119350; 333159</t>
+          <t>273081; 325694</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>293813; 553292</t>
+          <t>512650; 589782</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>589780</t>
+          <t>689096</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>632832</t>
+          <t>728424</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1222613</t>
+          <t>1417520</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>265495; 807258</t>
+          <t>666230; 707029</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>617646; 645979</t>
+          <t>709782; 744317</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>742432; 1443239</t>
+          <t>1386029; 1443469</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1264515</t>
+          <t>1441509</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1403489</t>
+          <t>1540497</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2668004</t>
+          <t>2982006</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>985624; 1385169</t>
+          <t>1375418; 1505660</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1150352; 1537056</t>
+          <t>1486416; 1595252</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2346364; 2875222</t>
+          <t>2894695; 3059329</t>
         </is>
       </c>
     </row>
